--- a/Examples/bdtocb_csc_extract.xlsx
+++ b/Examples/bdtocb_csc_extract.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -400,6 +400,815 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Time (seconds)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>calUnitsColumnIndex</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>XColumnName</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Raw Heat Rate (</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>YColumnName</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>cal / s)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>areaTable</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024/12/173:26:27RUVMVEJXRN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>baselineTable</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024/12/173:26:27UAIMUDYIRC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>irTable</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024/12/173:26:27GFGUYRWQXT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>originalIRTable</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024/12/173:26:27MWSBBGKMAI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>injVolTable</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024/12/173:26:27WELRPWQZIA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IsUnfilteredData</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Titrant</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Titrate</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>InitalTitrateVolume</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>HeatRateOffset</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>-162.770378253057</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>starttime</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>638670959266465956</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>equilseconds</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>integrationRegionStart</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>integrationRegionWidth</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>integrationRegionInterval</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>numRegions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Matched with lookahead offset 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AutoCreateBaseline</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UserName</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>StirRate</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Matched with lookahead offset 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ExothermUp</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ContinousTitration</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FirstInjStartTime</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>analysisType</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>InjectionByInjection</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PartiallyFilledCell</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DefaultInjVolume</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TotalContInjVolume</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ConstantSubtraction</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Token did not match expected type</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BlankSubtractType</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2024/12/173:26:39IJYMWDVWJP</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>bUseDefaultInjVolume</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>rgraphTable</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ModelFitSettings</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bBaselineExists</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>bValidAnalysisForBatch</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>bValidExperimentParams</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>bFitClosenessCriteriaMet</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FitModels</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ConfidenceSettings</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NumModels</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ITCResultsLog</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MicroCalories</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>No remaining token</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -407,7 +1216,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -460,10 +1269,10 @@
         <v>300</v>
       </c>
       <c r="C2">
-        <v>409</v>
+        <v>500</v>
       </c>
       <c r="D2">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="E2">
         <v>300</v>
@@ -486,10 +1295,10 @@
         <v>500</v>
       </c>
       <c r="C3">
-        <v>610</v>
+        <v>700</v>
       </c>
       <c r="D3">
-        <v>110</v>
+        <v>200</v>
       </c>
       <c r="E3">
         <v>500</v>
@@ -512,10 +1321,10 @@
         <v>700</v>
       </c>
       <c r="C4">
-        <v>809</v>
+        <v>900</v>
       </c>
       <c r="D4">
-        <v>109</v>
+        <v>200</v>
       </c>
       <c r="E4">
         <v>700</v>
@@ -538,10 +1347,10 @@
         <v>900</v>
       </c>
       <c r="C5">
-        <v>1023</v>
+        <v>1100</v>
       </c>
       <c r="D5">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="E5">
         <v>900</v>
@@ -564,10 +1373,10 @@
         <v>1100</v>
       </c>
       <c r="C6">
-        <v>1208</v>
+        <v>1300</v>
       </c>
       <c r="D6">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="E6">
         <v>1100</v>
@@ -590,10 +1399,10 @@
         <v>1300</v>
       </c>
       <c r="C7">
-        <v>1413</v>
+        <v>1500</v>
       </c>
       <c r="D7">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="E7">
         <v>1300</v>
@@ -616,10 +1425,10 @@
         <v>1500</v>
       </c>
       <c r="C8">
-        <v>1623</v>
+        <v>1700</v>
       </c>
       <c r="D8">
-        <v>123</v>
+        <v>200</v>
       </c>
       <c r="E8">
         <v>1500</v>
@@ -642,10 +1451,10 @@
         <v>1700</v>
       </c>
       <c r="C9">
-        <v>1821</v>
+        <v>1900</v>
       </c>
       <c r="D9">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="E9">
         <v>1700</v>
@@ -668,10 +1477,10 @@
         <v>1900</v>
       </c>
       <c r="C10">
-        <v>2020</v>
+        <v>2100</v>
       </c>
       <c r="D10">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E10">
         <v>1900</v>
@@ -694,10 +1503,10 @@
         <v>2100</v>
       </c>
       <c r="C11">
-        <v>2224</v>
+        <v>2300</v>
       </c>
       <c r="D11">
-        <v>124</v>
+        <v>200</v>
       </c>
       <c r="E11">
         <v>2100</v>
@@ -720,10 +1529,10 @@
         <v>2300</v>
       </c>
       <c r="C12">
-        <v>2441</v>
+        <v>2500</v>
       </c>
       <c r="D12">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="E12">
         <v>2300</v>
@@ -746,10 +1555,10 @@
         <v>2500</v>
       </c>
       <c r="C13">
-        <v>2653</v>
+        <v>2700</v>
       </c>
       <c r="D13">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="E13">
         <v>2500</v>
@@ -772,10 +1581,10 @@
         <v>2700</v>
       </c>
       <c r="C14">
-        <v>2887</v>
+        <v>2900</v>
       </c>
       <c r="D14">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E14">
         <v>2700</v>
@@ -798,10 +1607,10 @@
         <v>2900</v>
       </c>
       <c r="C15">
-        <v>3041</v>
+        <v>3100</v>
       </c>
       <c r="D15">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="E15">
         <v>2900</v>
@@ -824,10 +1633,10 @@
         <v>3100</v>
       </c>
       <c r="C16">
-        <v>3198</v>
+        <v>3300</v>
       </c>
       <c r="D16">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="E16">
         <v>3100</v>
@@ -850,10 +1659,10 @@
         <v>3300</v>
       </c>
       <c r="C17">
-        <v>3403</v>
+        <v>3500</v>
       </c>
       <c r="D17">
-        <v>103</v>
+        <v>200</v>
       </c>
       <c r="E17">
         <v>3300</v>
@@ -876,10 +1685,10 @@
         <v>3500</v>
       </c>
       <c r="C18">
-        <v>3613</v>
+        <v>3700</v>
       </c>
       <c r="D18">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="E18">
         <v>3500</v>
@@ -902,10 +1711,10 @@
         <v>3700</v>
       </c>
       <c r="C19">
-        <v>3808</v>
+        <v>3900</v>
       </c>
       <c r="D19">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="E19">
         <v>3700</v>
@@ -928,10 +1737,10 @@
         <v>3900</v>
       </c>
       <c r="C20">
-        <v>4011</v>
+        <v>4100</v>
       </c>
       <c r="D20">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="E20">
         <v>3900</v>
@@ -954,10 +1763,10 @@
         <v>4100</v>
       </c>
       <c r="C21">
-        <v>4197</v>
+        <v>4300</v>
       </c>
       <c r="D21">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="E21">
         <v>4100</v>
@@ -969,6 +1778,526 @@
         <v>200</v>
       </c>
       <c r="H21">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>4300</v>
+      </c>
+      <c r="C22">
+        <v>4500</v>
+      </c>
+      <c r="D22">
+        <v>200</v>
+      </c>
+      <c r="E22">
+        <v>4300</v>
+      </c>
+      <c r="F22">
+        <v>4500</v>
+      </c>
+      <c r="G22">
+        <v>200</v>
+      </c>
+      <c r="H22">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>4500</v>
+      </c>
+      <c r="C23">
+        <v>4700</v>
+      </c>
+      <c r="D23">
+        <v>200</v>
+      </c>
+      <c r="E23">
+        <v>4500</v>
+      </c>
+      <c r="F23">
+        <v>4700</v>
+      </c>
+      <c r="G23">
+        <v>200</v>
+      </c>
+      <c r="H23">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>4700</v>
+      </c>
+      <c r="C24">
+        <v>4900</v>
+      </c>
+      <c r="D24">
+        <v>200</v>
+      </c>
+      <c r="E24">
+        <v>4700</v>
+      </c>
+      <c r="F24">
+        <v>4900</v>
+      </c>
+      <c r="G24">
+        <v>200</v>
+      </c>
+      <c r="H24">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>4900</v>
+      </c>
+      <c r="C25">
+        <v>5100</v>
+      </c>
+      <c r="D25">
+        <v>200</v>
+      </c>
+      <c r="E25">
+        <v>4900</v>
+      </c>
+      <c r="F25">
+        <v>5100</v>
+      </c>
+      <c r="G25">
+        <v>200</v>
+      </c>
+      <c r="H25">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>5100</v>
+      </c>
+      <c r="C26">
+        <v>5300</v>
+      </c>
+      <c r="D26">
+        <v>200</v>
+      </c>
+      <c r="E26">
+        <v>5100</v>
+      </c>
+      <c r="F26">
+        <v>5300</v>
+      </c>
+      <c r="G26">
+        <v>200</v>
+      </c>
+      <c r="H26">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>5300</v>
+      </c>
+      <c r="C27">
+        <v>5500</v>
+      </c>
+      <c r="D27">
+        <v>200</v>
+      </c>
+      <c r="E27">
+        <v>5300</v>
+      </c>
+      <c r="F27">
+        <v>5500</v>
+      </c>
+      <c r="G27">
+        <v>200</v>
+      </c>
+      <c r="H27">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>5500</v>
+      </c>
+      <c r="C28">
+        <v>5700</v>
+      </c>
+      <c r="D28">
+        <v>200</v>
+      </c>
+      <c r="E28">
+        <v>5500</v>
+      </c>
+      <c r="F28">
+        <v>5700</v>
+      </c>
+      <c r="G28">
+        <v>200</v>
+      </c>
+      <c r="H28">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>5700</v>
+      </c>
+      <c r="C29">
+        <v>5900</v>
+      </c>
+      <c r="D29">
+        <v>200</v>
+      </c>
+      <c r="E29">
+        <v>5700</v>
+      </c>
+      <c r="F29">
+        <v>5900</v>
+      </c>
+      <c r="G29">
+        <v>200</v>
+      </c>
+      <c r="H29">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>5900</v>
+      </c>
+      <c r="C30">
+        <v>6100</v>
+      </c>
+      <c r="D30">
+        <v>200</v>
+      </c>
+      <c r="E30">
+        <v>5900</v>
+      </c>
+      <c r="F30">
+        <v>6100</v>
+      </c>
+      <c r="G30">
+        <v>200</v>
+      </c>
+      <c r="H30">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>6100</v>
+      </c>
+      <c r="C31">
+        <v>6300</v>
+      </c>
+      <c r="D31">
+        <v>200</v>
+      </c>
+      <c r="E31">
+        <v>6100</v>
+      </c>
+      <c r="F31">
+        <v>6300</v>
+      </c>
+      <c r="G31">
+        <v>200</v>
+      </c>
+      <c r="H31">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>6300</v>
+      </c>
+      <c r="C32">
+        <v>6500</v>
+      </c>
+      <c r="D32">
+        <v>200</v>
+      </c>
+      <c r="E32">
+        <v>6300</v>
+      </c>
+      <c r="F32">
+        <v>6500</v>
+      </c>
+      <c r="G32">
+        <v>200</v>
+      </c>
+      <c r="H32">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>6500</v>
+      </c>
+      <c r="C33">
+        <v>6700</v>
+      </c>
+      <c r="D33">
+        <v>200</v>
+      </c>
+      <c r="E33">
+        <v>6500</v>
+      </c>
+      <c r="F33">
+        <v>6700</v>
+      </c>
+      <c r="G33">
+        <v>200</v>
+      </c>
+      <c r="H33">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>6700</v>
+      </c>
+      <c r="C34">
+        <v>6900</v>
+      </c>
+      <c r="D34">
+        <v>200</v>
+      </c>
+      <c r="E34">
+        <v>6700</v>
+      </c>
+      <c r="F34">
+        <v>6900</v>
+      </c>
+      <c r="G34">
+        <v>200</v>
+      </c>
+      <c r="H34">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>6900</v>
+      </c>
+      <c r="C35">
+        <v>7100</v>
+      </c>
+      <c r="D35">
+        <v>200</v>
+      </c>
+      <c r="E35">
+        <v>6900</v>
+      </c>
+      <c r="F35">
+        <v>7100</v>
+      </c>
+      <c r="G35">
+        <v>200</v>
+      </c>
+      <c r="H35">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>7100</v>
+      </c>
+      <c r="C36">
+        <v>7300</v>
+      </c>
+      <c r="D36">
+        <v>200</v>
+      </c>
+      <c r="E36">
+        <v>7100</v>
+      </c>
+      <c r="F36">
+        <v>7300</v>
+      </c>
+      <c r="G36">
+        <v>200</v>
+      </c>
+      <c r="H36">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>7300</v>
+      </c>
+      <c r="C37">
+        <v>7500</v>
+      </c>
+      <c r="D37">
+        <v>200</v>
+      </c>
+      <c r="E37">
+        <v>7300</v>
+      </c>
+      <c r="F37">
+        <v>7500</v>
+      </c>
+      <c r="G37">
+        <v>200</v>
+      </c>
+      <c r="H37">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>7500</v>
+      </c>
+      <c r="C38">
+        <v>7700</v>
+      </c>
+      <c r="D38">
+        <v>200</v>
+      </c>
+      <c r="E38">
+        <v>7500</v>
+      </c>
+      <c r="F38">
+        <v>7700</v>
+      </c>
+      <c r="G38">
+        <v>200</v>
+      </c>
+      <c r="H38">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>7700</v>
+      </c>
+      <c r="C39">
+        <v>7900</v>
+      </c>
+      <c r="D39">
+        <v>200</v>
+      </c>
+      <c r="E39">
+        <v>7700</v>
+      </c>
+      <c r="F39">
+        <v>7900</v>
+      </c>
+      <c r="G39">
+        <v>200</v>
+      </c>
+      <c r="H39">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>7900</v>
+      </c>
+      <c r="C40">
+        <v>8100</v>
+      </c>
+      <c r="D40">
+        <v>200</v>
+      </c>
+      <c r="E40">
+        <v>7900</v>
+      </c>
+      <c r="F40">
+        <v>8100</v>
+      </c>
+      <c r="G40">
+        <v>200</v>
+      </c>
+      <c r="H40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>8100</v>
+      </c>
+      <c r="C41">
+        <v>8300</v>
+      </c>
+      <c r="D41">
+        <v>200</v>
+      </c>
+      <c r="E41">
+        <v>8100</v>
+      </c>
+      <c r="F41">
+        <v>8300</v>
+      </c>
+      <c r="G41">
+        <v>200</v>
+      </c>
+      <c r="H41">
         <v>2.5</v>
       </c>
     </row>
